--- a/4p-index/STP_Lei-8-2020_Plastic-Bag-Law_4P-Index.xlsx
+++ b/4p-index/STP_Lei-8-2020_Plastic-Bag-Law_4P-Index.xlsx
@@ -588,61 +588,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E2" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
@@ -654,25 +640,19 @@
           <t>Art. 1.º: 'A presente Lei tem por objecto a proibição da produção, importação, comercialização e distribuição de sacos de plástico não biodegradáveis no Território Nacional.' / 'This Law has as its object the prohibition of the production, importation, marketing and distribution of non-biodegradable plastic bags in National Territory.' Art. 7.º(1): 'Fica proibida a produção artesanal ou industrial de sacos de plástico convencionais no Território Nacional, após a entrada em vigor do presente Diploma.' / 'The artisanal or industrial production of conventional plastic bags in National Territory is prohibited, after the entry into force of this Decree.' Art. 7.º(2): 'Para efeitos do presente Diploma, a produção de sacos de plástico inclui a reciclagem e o processamento de produtos cujo composto químico seja igual ao dos plásticos proibidos.' / 'For the purposes of this Decree, the production of plastic bags includes the recycling and processing of products whose chemical compound is the same as that of the prohibited plastics.' Art. 19.º(1) reiterates the prohibition; Art. 20.º sets the sanction (see implementation text).</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 16.º designates the 'Direcção de Regulação e Controlo das Actividades Económicas' and Local Authorities (São Tomé) / regional administration services (RAP) as the supervisory competence for this and other prohibitions (+0.25). Enforcement: Art. 20.º: 'A produção ilegal ou clandestina de sacos de plástico... é punida com coima de 10.000,00 a 45.000,00 dobras. Cumulativamente, é aplicada a sanção assessória de encerramento do local de produção e perda dos objectos e utensílios utilizados na produção a favor do Estado.' / 'Illegal or clandestine production of plastic bags... is punished with a fine of 10,000 to 45,000 dobras. Cumulatively, the accessory sanction of closure of the production site and forfeiture to the State of the objects and tools used in production is applied.' (+0.25). Monitoring: Art. 26.º(a): the Directorate-General for the Environment must 'Requerer estatísticas das importações e da venda' / 'Request import and sales statistics' semi-annually (+0.25). Not unconditional: Art. 27.º grants economic operators a 6-month grace period from entry into force to exhaust existing stocks and prior orders (0).</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
+      <c r="V2" s="2" t="n">
+        <v>0.875</v>
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
@@ -701,61 +681,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E3" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F3" s="2" t="inlineStr"/>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
@@ -767,25 +733,19 @@
           <t>Art. 8.º: 'Fica proibida a importação dos sacos de plástico convencionais, conforme definido na alínea b) do artigo 3.º, 180 dias após a entrada em vigor do presente Diploma.' / 'The importation of conventional plastic bags, as defined in Article 3(b), is prohibited 180 days after the entry into force of this Decree.' Art. 19.º(1) reiterates the prohibition; Art. 21.º sets the enforcement route.</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 16.º(3): customs infractions fall under the competence of the legally competent bodies (customs authorities) under general terms (+0.25). Enforcement: Art. 21.º: 'A importação de sacos de plástico não biodegradáveis é uma infracção aduaneira registada, processada e punida de acordo com as disposições do Código Aduaneiro.' / 'The importation of non-biodegradable plastic bags is a customs infraction registered, processed and punished in accordance with the provisions of the Customs Code.' (+0.25). Monitoring: Art. 26.º(a) requires semi-annual import statistics (+0.25). Not unconditional: the ban only takes effect 180 days after entry into force, and Art. 27.º grants a further 6-month stock/order grace period (0).</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
+      <c r="V3" s="2" t="n">
+        <v>0.875</v>
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
@@ -814,61 +774,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
@@ -880,25 +826,19 @@
           <t>Art. 1.º and Art. 19.º(1) prohibit the 'comercialização' (marketing/commercialisation) of non-biodegradable plastic bags in National Territory, alongside production, importation and distribution. Art. 22.º: 'A comercialização de sacos de plásticos não biodegradáveis é punível com coima de 10.000,00 dobras a 100.000,00 dobras, quando praticada por pessoa colectiva é aplicada a penalidade máxima.' / 'The marketing of non-biodegradable plastic bags is punishable by a fine of 10,000 to 100,000 dobras; when committed by a legal person, the maximum penalty is applied.'</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 16.º/17.º designate the Directorate of Regulation and Control of Economic Activities and Local Authorities (São Tomé) / regional services (RAP) as competent for supervision and sanctions (+0.25). Enforcement: Art. 22.º's explicit fine, escalating to the maximum penalty for legal entities (+0.25). Monitoring: Art. 26.º(a) sales statistics requirement (+0.25). Not unconditional: the Art. 27.º 6-month stock-depletion grace period applies to marketing as well as production/import (0).</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
+      <c r="V4" s="2" t="n">
+        <v>0.875</v>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
@@ -927,61 +867,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E5" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O5" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P5" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
@@ -993,25 +919,19 @@
           <t>Art. 9.º(1): 'A importação de sacos de plástico abrangidos pelo presente Diploma fica sujeita, a partir de 1 de Janeiro de 2021, a uma taxa aduaneira agravada.' / 'The importation of plastic bags covered by this Decree is subject, from 1 January 2021, to an increased customs duty.' Art. 9.º(2): the duty is fixed at '20% do valor CIF' / '20% of the CIF value'. Art. 9.º(3): 'A aplicação dessa taxa está limitada no tempo e cessa com a entrada em vigor da proibição da importação prevista no artigo anterior.' / 'Application of this duty is time-limited and ceases upon the entry into force of the import prohibition provided for in the preceding article.'</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
           <t>Authority: implicitly the customs administration, consistent with Art. 16.º(3) (+0.25). No enforcement sub-score — this is a standard customs duty, not a penalty for non-compliance (0). Monitoring: Art. 26.º(a) import statistics (+0.25). Not unconditional: the duty is explicitly time-limited and self-terminating once the import ban (Row 2) takes effect (Art. 9.º(3)) (0).</t>
         </is>
       </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V5" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
@@ -1040,61 +960,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E6" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O6" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
@@ -1106,25 +1012,19 @@
           <t>Art. 10.º(1): 'O direito aduaneiro cobrado na importação de sacos de plástico degradáveis e biodegradáveis, bem como dos produtos alternativos constantes do Anexo I, é fixado com a taxa aduaneira mínima de 5% do valor CIF.' / 'The customs duty charged on the importation of degradable and biodegradable plastic bags, as well as the alternative products listed in Annex I, is fixed at the minimum customs rate of 5% of CIF value.' Art. 10.º(2): 'O Governo deve criar o quadro regulamentar de incentivos económicos e administrativos para os investimentos privados destinados à produção e comercialização, no Território Nacional, dos produtos alternativos contidos no Anexo I.' / 'The Government shall create the regulatory framework of economic and administrative incentives for private investment in the production and marketing, within National Territory, of the alternative products listed in Annex I.' Annex I lists: paper bags (with/without handles); plastic bags derived from plant/animal-origin products; photosensitive plastic bags; jute bags (with handles); cotton bags (cloth); raffia bags (with handles); and recycled PET (polyethylene terephthalate) sacks.</t>
         </is>
       </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 10.º(1) ties the reduced rate to a 'despacho dos Ministros encarregues das áreas das Finanças e do Ambiente' / 'order of the Ministers responsible for Finance and the Environment' (+0.25). No enforcement sub-score — this is a positive economic incentive, not a penalty (0). Monitoring: Art. 26.º(d): 'Estudar e propor os mecanismos de certificação dos produtos alternativos importados' / 'Study and propose certification mechanisms for imported alternative products' (+0.25). Not unconditional: Art. 10.º(2)'s broader incentive framework is a mandatory duty on the Government ('deve criar') but is not itself shown, in the text located, to have already been established (0).</t>
         </is>
       </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V6" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
@@ -1153,61 +1053,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
@@ -1219,25 +1105,19 @@
           <t>Art. 11.º(1): 'Fica proibida a distribuição gratuita de qualquer tipo de sacos de plástico por todos os agentes económicos localizados em Território Nacional.' / 'The free distribution of any type of plastic bag by all economic agents located in National Territory is prohibited.' Art. 11.º(2): 'A distribuição gratuita abrange todas as formas de fornecimento de sacos de plástico convencionais, incluindo a embalagem de produtos para a venda a retalho, bem como a distribuição dos sacos como material promocional.' / 'Free distribution covers all forms of supply of conventional plastic bags, including the packaging of products for retail sale, as well as the distribution of bags as promotional material.' Art. 23.º sets the sanction (see implementation text).</t>
         </is>
       </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 16.º/17.º framework (+0.25). Enforcement: Art. 23.º(1): 'A distribuição gratuita de sacos de plástico em violação do disposto no presente Diploma é punida com coima de 1.100,00 dobras, no caso de pessoas singulares, e 7.500,00 dobras, no caso de pessoas colectivas.' / 'Free distribution of plastic bags in violation of this Decree is punished with a fine of 1,100 dobras for individuals and 7,500 dobras for legal entities.' Art. 23.º(2): repeat offences incur higher fines (2,500/25,000 dobras) 'acrescida da perda a favor do Estado de todos os sacos de plástico armazenados pelo infractor' / 'plus forfeiture to the State of all plastic bags stored by the offender' (+0.25). Monitoring: Art. 26.º(b): 'Requerer dados da aplicação das sanções' / 'Request data on the application of sanctions' (+0.25). Not unconditional: the general 6-month stock grace period (Art. 27.º) applies (0).</t>
         </is>
       </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0.875</t>
-        </is>
+      <c r="V7" s="2" t="n">
+        <v>0.875</v>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
@@ -1266,61 +1146,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P8" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
@@ -1332,25 +1198,19 @@
           <t>Art. 12.º: 'De modo a permitir a redução gradual do consumo de sacos de plástico pelo Governo Central, Governo Regional e as Autarquias Locais, fica vedada após entrada em vigor do presente Diploma, a distribuição gratuita de sacos de plástico pelos serviços públicos a estes afectos.' / 'In order to allow for the gradual reduction of plastic-bag consumption by the Central Government, Regional Government and Local Authorities, the free distribution of plastic bags by the public services attached to them is prohibited following the entry into force of this Decree.'</t>
         </is>
       </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
           <t>Authority: the general Art. 16.º/17.º supervisory framework is not explicitly carved out from applying to public bodies, so the same competent entities apply (+0.25). No specific enforcement sanction is set out for public-sector non-compliance with this article itself (0). No monitoring mechanism specifically tied to public-sector compliance is identified (0). Unconditional: no exemption is stated for this obligation (+0.25).</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="V8" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
@@ -1379,61 +1239,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M9" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0.88</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+      <c r="O9" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P9" s="2" t="n">
+        <v>0.4</v>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
@@ -1445,25 +1291,19 @@
           <t>Art. 6.º: 'São adoptadas acções de sensibilização para a redução do uso de sacos de plástico convencionais.' / 'Awareness-raising actions for the reduction of conventional plastic-bag use are adopted.' Art. 13.º: 'Os organismos públicos da administração central, regional e local devem promover acções de sensibilização sectorial, com o objectivo de promover a redução do uso de sacos de plástico... e a utilização de produtos alternativos', targeting: (a) the Chamber of Commerce, Industry, Agriculture and Services; (b) merchant associations; (c) the hospitality and restaurant sector; (d) consumer associations; and (e) the general public. Art. 15.º commits Government funding for these actions (see policy-level budget, Column N).</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 13.º explicitly designates central, regional and local public administration bodies as responsible, targeting five named stakeholder groups (+0.25). No enforcement sub-score — awareness campaigns are not backed by penalties (0). Monitoring: Art. 26.º(e): 'Elaborar relatórios semestrais sobre a evolução dos objectivos de redução previamente fixados' / 'Prepare semi-annual reports on progress towards the previously set reduction objectives' (+0.25). Unconditional: no exemptions are stated for this obligation (+0.25).</t>
         </is>
       </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0.575</t>
-        </is>
+      <c r="V9" s="2" t="n">
+        <v>0.575</v>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
@@ -1492,61 +1332,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="2" t="inlineStr"/>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M10" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O10" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P10" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
@@ -1558,25 +1384,19 @@
           <t>Art. 14.º: 'Cabe ao Governo, através dos serviços públicos do Estado, das Autarquias Locais e da Região Autónoma do Príncipe, implementar a recolha selectiva de material e resíduos de plásticos, de modo a evitar a sua libertação no ambiente.' / 'It is incumbent upon the Government, through State public services, Local Authorities and the Autonomous Region of Príncipe, to implement the selective collection of plastic material and waste, so as to prevent its release into the environment.'</t>
         </is>
       </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
           <t>Authority: central government (State public services), Local Authorities and the Príncipe regional government are all explicitly named as joint implementers (+0.25). No enforcement sub-score — this is a positive service-delivery obligation, not penalty-backed (0). No monitoring mechanism specifically tied to selective-collection coverage/rates is identified in the text located (Art. 26.º does not explicitly mention it) (0). Unconditional: no exemption is stated (+0.25).</t>
         </is>
       </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0.35</t>
-        </is>
+      <c r="V10" s="2" t="n">
+        <v>0.35</v>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
@@ -1605,61 +1425,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E11" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="inlineStr"/>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M11" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O11" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P11" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
@@ -1671,25 +1477,19 @@
           <t>Art. 16.º(1): 'Em São Tomé, a competência fiscalizadora cabe à Direcção de Regulação e Controlo das Actividades Económicas, bem como às Autarquias Locais, dentro das respectivas jurisdições e de acordo com as suas competências.' / 'In São Tomé, supervisory competence rests with the Directorate of Regulation and Control of Economic Activities, as well as Local Authorities, within their respective jurisdictions and in accordance with their competences.' Art. 16.º(2): 'Na Região Autónoma do Príncipe, a competência fiscalizadora cabe aos serviços competentes da administração regional.' / 'In the Autonomous Region of Príncipe, supervisory competence rests with the competent services of the regional administration.' Art. 16.º(3): customs infractions are handled by the legally competent customs bodies, unless detected through the supervision described above, in which case the citing body must forward the matter to the competent sector. Art. 17.º: 'Salvo o disposto na parte final do n.º 3 do artigo anterior, a competência sancionatória cabe sempre à entidade competente para a fiscalização.' / 'Except as provided in the final part of paragraph 3 of the preceding article, sanctioning competence always rests with the entity competent for supervision.'</t>
         </is>
       </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
           <t>Authority: this article itself explicitly establishes the competent supervisory bodies across national (São Tomé), regional (Príncipe) and customs levels (+0.25). Enforcement: Art. 17.º confirms that sanctioning competence follows supervisory competence, i.e. these bodies also hold sanctioning power (+0.25). No separate monitoring mechanism within these two articles themselves (Art. 26.º is coded separately, Row 13) (0). Unconditional: no exemptions are stated to this competence allocation (+0.25).</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0.475</t>
-        </is>
+      <c r="V11" s="2" t="n">
+        <v>0.475</v>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
@@ -1718,61 +1518,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E12" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="2" t="inlineStr"/>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M12" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>0.6</t>
-        </is>
+      <c r="O12" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="P12" s="2" t="n">
+        <v>0.6</v>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
@@ -1784,25 +1570,19 @@
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned as follows: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.'</t>
         </is>
       </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+      <c r="S12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" s="2" t="n">
+        <v>0.5</v>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Authority: the four beneficiary entities (Treasury, Competent Entity, Environmental Fund, citing agent) are explicitly named (+0.25). No enforcement sub-score applicable to a revenue-allocation rule (0). No monitoring mechanism specified for tracking disbursement (0). Unconditional: the percentages are fixed with no stated exceptions (+0.25).</t>
         </is>
       </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+      <c r="V12" s="2" t="n">
+        <v>0.55</v>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
@@ -1831,61 +1611,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E13" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="2" t="inlineStr"/>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="O13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
@@ -1897,25 +1663,19 @@
           <t>Art. 19.º(2): 'É também proibido/interdito qualquer abandono de sacos ou embalagens de plásticos não biodegradáveis nas vias públicas, nos arredores das habitações, no meio urbano e rural, nas redes de esgotos, nos cursos de água, no mar e nas praias ou em locais que não sejam autorizados pelas autoridades públicas competentes.' / 'Also prohibited is any abandonment of non-biodegradable plastic bags or packaging on public roads, around dwellings, in urban and rural environments, in sewage networks, in watercourses, in the sea and on beaches, or at locations not authorised by the competent public authorities.' Art. 24.º sets the sanction: 'A rejeição de sacos de plástico, em lugares que não sejam nos pontos de colecta ou recuperação previstos para este fim, é punida com coima de 1.000 a 30.000 dobras.' / 'The rejection of plastic bags at locations other than designated collection or recovery points is punished with a fine of 1,000 to 30,000 dobras.'</t>
         </is>
       </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="S13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Authority: Art. 16.º/17.º framework applies (+0.25). Enforcement: Art. 24.º's explicit fine (+0.25). Monitoring: Art. 26.º(b) requires data on sanctions applied, which would capture littering infractions (+0.25). Unconditional: no exemption or grace period is stated for this prohibition (unlike the production/import/marketing bans, the littering ban is not tied to existing-stock depletion under Art. 27.º) (+0.25).</t>
         </is>
       </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="V13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
@@ -1944,61 +1704,47 @@
           <t>Prohibits the production, importation, marketing and free distribution of non-biodegradable ('conventional') plastic bags in national territory, requiring substitution with paper, cloth, jute, raffia, recycled PET or other certified biodegradable/photosensitive alternatives (Annex I). Combines market-based measures (bans, a temporary increased import tariff, a reduced tariff and incentive framework for alternatives) with awareness-raising actions, selective collection of plastic waste, and multi-level enforcement coordination (national, Príncipe regional and municipal/local authorities) to reduce plastic bag pollution of residential, agricultural, coastal and freshwater environments and its public-health impacts, in fulfilment of an international commitment referenced in the preamble.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="E14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="2" t="inlineStr"/>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t>Act of Parliament — 'a Assembleia Nacional, no uso das faculdades conferidas pela alínea b) do artigo 97.º da Constituição, decreta o seguinte' / 'the National Assembly, in the exercise of the power conferred by paragraph (b) of Article 97 of the Constitution, decrees the following' — approved in final global vote on 11 August 2020 and promulgated by the President of the Republic on 4 September 2020. This is primary legislation, not an executive decree or ministerial regulation.</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
           <t>retail/commerce, trade/customs, environment, tourism, agriculture, industry, municipalities, fisheries, waste management, public health</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>production, consumption, recycling, disposal, environmental leakage</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="M14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>Art. 18.º: 'As coimas cobradas ao abrigo do presente Diploma são repartidas nas seguintes proporções: a) Tesouro Público: 60%; b) Entidade Competente: 15%; c) Fundo do Ambiente: 15%; d) Agente autuante: 10%.' / 'Fines collected under this Decree are apportioned in the following proportions: (a) Public Treasury: 60%; (b) Competent Entity: 15%; (c) Environmental Fund: 15%; (d) Citing agent: 10%.' Art. 15.º: 'Cabe ao Governo assegurar os recursos financeiros para a realização das despesas decorrentes das acções de sensibilização previstas na presente secção.' / 'It is incumbent upon the Government to ensure the financial resources for expenses arising from the awareness-raising actions provided for in this section.'</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+      <c r="O14" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P14" s="2" t="n">
+        <v>0.2</v>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
@@ -2010,25 +1756,19 @@
           <t>Art. 26.º: 'A Direcção-geral do Ambiente, em concertação com as Direcções das Alfândegas e do Comércio, estabelece mecanismos de seguimento semestral para a implementação da presente Lei, devendo: a) Requerer estatísticas das importações e da venda; b) Requerer dados da aplicação das sanções; c) Propor ao Ministro encarregue da área do Ambiente medidas adicionais para aplicação das disposições do presente Diploma; d) Estudar e propor os mecanismos de certificação dos produtos alternativos importados; e) Elaborar relatórios semestrais sobre a evolução dos objectivos de redução previamente fixados; f) Propor recomendações visando à revisão do presente Diploma.' / 'The Directorate-General for the Environment, in coordination with the Customs and Commerce Directorates, shall establish semi-annual follow-up mechanisms for the implementation of this Law, and shall: (a) request import and sales statistics; (b) request data on the application of sanctions; (c) propose additional measures to the Minister responsible for the Environment for the application of this Decree's provisions; (d) study and propose certification mechanisms for imported alternative products; (e) prepare semi-annual reports on the progress of previously set reduction objectives; and (f) propose recommendations for revising this Decree.'</t>
         </is>
       </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
+      <c r="S14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>0.75</v>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Authority: the Directorate-General for the Environment, Customs Directorate and Commerce Directorate are explicitly named as joint implementers (+0.25). No enforcement sub-score — this is the monitoring instrument itself, not a penalty (0). Monitoring: this article itself establishes a comprehensive semi-annual data-collection and reporting mechanism (+0.25). Unconditional: no exemptions are stated to this obligation (+0.25).</t>
         </is>
       </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0.475</t>
-        </is>
+      <c r="V14" s="2" t="n">
+        <v>0.475</v>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
